--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -20402,13 +20402,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O104" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="R104" t="n">
-        <v>1.761021079155496</v>
+        <v>1.81438535428142</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20566,10 +20566,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O105" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -20911,12 +20911,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -20941,7 +20941,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -20950,16 +20950,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>1.102695890537435</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -20968,12 +20965,12 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -20983,7 +20980,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -20991,57 +20988,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21073,12 +21075,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -21103,7 +21105,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -21112,32 +21114,29 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>TBE</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -21147,12 +21146,12 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
@@ -21162,7 +21161,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
@@ -21177,7 +21176,7 @@
       </c>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG108" t="inlineStr">
@@ -21197,17 +21196,17 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM TBE disease category.</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -21220,7 +21219,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
@@ -21228,57 +21227,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21340,7 +21344,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -21502,7 +21506,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -21739,7 +21743,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -21901,7 +21905,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -22138,7 +22142,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -22300,7 +22304,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -22507,12 +22511,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -22537,22 +22541,25 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.03557618341728275</v>
+        <v>0</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -22561,12 +22568,12 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -22576,70 +22583,65 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22671,12 +22673,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -22701,38 +22703,41 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>TBE (tick borne encephalitis)</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -22742,12 +22747,12 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
@@ -22757,7 +22762,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -22772,7 +22777,7 @@
       </c>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG116" t="inlineStr">
@@ -22792,12 +22797,12 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -22815,70 +22820,65 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22910,118 +22910,521 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>6</v>
+      </c>
+      <c r="O117" t="n">
+        <v>6</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>6</v>
+      </c>
+      <c r="O118" t="n">
+        <v>6</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>D205</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
         <is>
           <t>蜱传脑炎</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N117" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="inlineStr">
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO117" t="inlineStr">
+      <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP117" t="inlineStr">
+      <c r="AP119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR117" t="inlineStr">
+      <c r="AR119" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS117" t="inlineStr"/>
-      <c r="AT117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV117" t="inlineStr">
+      <c r="AV119" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW117" t="inlineStr">
+      <c r="AW119" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
+      <c r="AX119" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY117" t="inlineStr">
+      <c r="AY119" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
+      <c r="AZ119" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA117" t="inlineStr">
+      <c r="BA119" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB117" t="inlineStr">
+      <c r="BB119" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC117" t="inlineStr">
+      <c r="BC119" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -23143,7 +23546,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -23153,7 +23556,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
@@ -23173,7 +23576,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -23205,7 +23608,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>957</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -22910,12 +22910,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -22940,22 +22940,25 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.1067285502518482</v>
+        <v>0</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -22964,12 +22967,12 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -22979,70 +22982,65 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23074,12 +23072,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -23104,38 +23102,41 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>TBE (tick borne encephalitis)</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -23145,12 +23146,12 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
@@ -23160,7 +23161,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -23175,7 +23176,7 @@
       </c>
       <c r="AF118" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG118" t="inlineStr">
@@ -23195,12 +23196,12 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -23218,70 +23219,65 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23313,118 +23309,521 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>7</v>
+      </c>
+      <c r="O119" t="n">
+        <v>7</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.1245166419604896</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>7</v>
+      </c>
+      <c r="O120" t="n">
+        <v>7</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>D205</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
         <is>
           <t>蜱传脑炎</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="K121" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N119" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="inlineStr">
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO119" t="inlineStr">
+      <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP119" t="inlineStr">
+      <c r="AP121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR119" t="inlineStr">
+      <c r="AR121" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS119" t="inlineStr"/>
-      <c r="AT119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV119" t="inlineStr">
+      <c r="AV121" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW119" t="inlineStr">
+      <c r="AW121" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
+      <c r="AX121" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY119" t="inlineStr">
+      <c r="AY121" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
+      <c r="AZ121" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA119" t="inlineStr">
+      <c r="BA121" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB119" t="inlineStr">
+      <c r="BB121" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC119" t="inlineStr">
+      <c r="BC121" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -23546,7 +23945,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -23556,7 +23955,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -23576,7 +23975,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -23608,7 +24007,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -23348,13 +23348,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O119" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R119" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -23512,10 +23512,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O120" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1083</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -23348,13 +23348,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O119" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R119" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.2668213756296206</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -23512,10 +23512,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O120" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1085</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -23348,13 +23348,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="O119" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="R119" t="n">
-        <v>0.2668213756296206</v>
+        <v>0.426914201007393</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -23512,10 +23512,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="O120" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -23826,6 +23826,405 @@
       <c r="BC121" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23862,7 +24261,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -23945,7 +24344,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -23955,7 +24354,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -23975,7 +24374,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -24007,7 +24406,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1091</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -11927,13 +11927,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O60" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R60" t="n">
-        <v>0.7437999830813258</v>
+        <v>0.721596998511734</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -15018,13 +15018,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O76" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R76" t="n">
-        <v>1.365483551029897</v>
+        <v>1.398788027884284</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -17710,13 +17710,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O90" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R90" t="n">
-        <v>1.121250720764387</v>
+        <v>1.143453705333978</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -18403,13 +18403,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O94" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R94" t="n">
-        <v>1.439111585955635</v>
+        <v>1.429766705527352</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -18567,10 +18567,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O95" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -20363,12 +20363,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -20402,100 +20402,81 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="O104" t="n">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="R104" t="n">
-        <v>1.81438535428142</v>
+        <v>0.2775373071198977</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_708</t>
-        </is>
-      </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_708</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -20522,7 +20503,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -20571,98 +20552,23 @@
       <c r="O105" t="n">
         <v>102</v>
       </c>
+      <c r="R105" t="n">
+        <v>1.81438535428142</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_708</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>TBE (tick borne encephalitis)</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD105" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE105" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG105" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN105" t="b">
-        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -20761,17 +20667,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -20805,81 +20711,175 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>102</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN106" t="b">
+        <v>1</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20911,12 +20911,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -20950,100 +20950,81 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>1.102695890537435</v>
+        <v>0</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TBE</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TBE</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21070,7 +21051,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -21114,103 +21095,28 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O108" t="n">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1.093351010109151</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TBE</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>TBE</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG108" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM TBE disease category.</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN108" t="b">
-        <v>1</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -21309,17 +21215,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -21344,7 +21250,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -21353,31 +21259,103 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>117</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>TBE</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM TBE disease category.</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN109" t="b">
+        <v>1</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -21386,7 +21364,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
@@ -21394,57 +21372,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21471,7 +21454,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -21523,98 +21506,23 @@
       <c r="P110" t="n">
         <v>0</v>
       </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG110" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN110" t="b">
-        <v>1</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -21708,7 +21616,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -21743,7 +21651,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -21760,23 +21668,98 @@
       <c r="P111" t="n">
         <v>0</v>
       </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
+        <v>1</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -21870,7 +21853,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -21922,98 +21905,23 @@
       <c r="P112" t="n">
         <v>0</v>
       </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -22107,7 +22015,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -22142,7 +22050,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -22159,23 +22067,98 @@
       <c r="P113" t="n">
         <v>0</v>
       </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN113" t="b">
+        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -22269,7 +22252,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -22321,98 +22304,23 @@
       <c r="P114" t="n">
         <v>0</v>
       </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE114" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF114" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG114" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN114" t="b">
-        <v>1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -22506,7 +22414,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -22541,7 +22449,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -22558,23 +22466,98 @@
       <c r="P115" t="n">
         <v>0</v>
       </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN115" t="b">
+        <v>1</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -22668,7 +22651,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -22720,98 +22703,23 @@
       <c r="P116" t="n">
         <v>0</v>
       </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN116" t="b">
-        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -22905,7 +22813,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -22940,7 +22848,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -22957,23 +22865,98 @@
       <c r="P117" t="n">
         <v>0</v>
       </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -23067,7 +23050,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -23119,98 +23102,23 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -23304,17 +23212,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -23339,37 +23247,115 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>24</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0.426914201007393</v>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN119" t="b">
+        <v>1</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -23378,70 +23364,65 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23468,7 +23449,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -23517,98 +23498,23 @@
       <c r="O120" t="n">
         <v>24</v>
       </c>
+      <c r="R120" t="n">
+        <v>0.426914201007393</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_708</t>
         </is>
       </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_708</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>TBE (tick borne encephalitis)</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -23707,17 +23613,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -23751,81 +23657,175 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23857,12 +23857,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -23887,7 +23887,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -23901,9 +23901,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -23912,82 +23909,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24014,7 +23997,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -24066,98 +24049,23 @@
       <c r="P123" t="n">
         <v>0</v>
       </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -24223,6 +24131,243 @@
         </is>
       </c>
       <c r="BC123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -24344,7 +24489,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -24354,7 +24499,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -24406,7 +24551,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1100</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -23493,13 +23493,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O120" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="R120" t="n">
-        <v>0.426914201007393</v>
+        <v>0.5336427512592412</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23657,10 +23657,10 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O121" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1126</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16760,7 +16760,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17159,7 +17159,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17855,13 +17855,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O91" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R91" t="n">
-        <v>1.778809170864138</v>
+        <v>1.743232987446855</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -18019,10 +18019,10 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O92" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19452,7 +19452,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21095,13 +21095,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O108" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R108" t="n">
-        <v>1.093351010109151</v>
+        <v>1.084006129680868</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21259,10 +21259,10 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O109" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22144,7 +22144,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22543,7 +22543,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22942,7 +22942,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -23493,13 +23493,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O120" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="R120" t="n">
-        <v>0.5336427512592412</v>
+        <v>0.9427688605579929</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23657,10 +23657,10 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O121" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24368,6 +24368,405 @@
         </is>
       </c>
       <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -24406,7 +24805,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -24489,7 +24888,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -24499,7 +24898,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
@@ -24519,7 +24918,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -24551,7 +24950,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1132</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -21095,13 +21095,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O108" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R108" t="n">
-        <v>1.084006129680868</v>
+        <v>1.074661249252585</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21259,10 +21259,10 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O109" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -23493,13 +23493,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="O120" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="R120" t="n">
-        <v>0.9427688605579929</v>
+        <v>1.191802144478972</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23657,10 +23657,10 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="O121" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -24769,6 +24769,953 @@
       <c r="BC126" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24805,7 +25752,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -24888,7 +25835,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -24898,7 +25845,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -24918,7 +25865,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -24950,7 +25897,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1152</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -23493,13 +23493,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="O120" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="R120" t="n">
-        <v>1.191802144478972</v>
+        <v>1.351894969856744</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23657,10 +23657,10 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="O121" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -25238,13 +25238,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R129" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -25402,10 +25402,10 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O130" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1166</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -25199,12 +25199,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -25229,22 +25229,25 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N129" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>0.07115236683456549</v>
+        <v>0</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -25253,12 +25256,12 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -25268,70 +25271,65 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25363,12 +25361,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -25393,38 +25391,41 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>TBE (tick borne encephalitis)</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -25434,12 +25435,12 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
@@ -25449,7 +25450,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -25464,7 +25465,7 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG130" t="inlineStr">
@@ -25484,12 +25485,12 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -25507,70 +25508,65 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25602,118 +25598,521 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>4</v>
+      </c>
+      <c r="O131" t="n">
+        <v>4</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.07115236683456549</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>4</v>
+      </c>
+      <c r="O132" t="n">
+        <v>4</v>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN132" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>D205</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
         <is>
           <t>蜱传脑炎</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="K133" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="inlineStr">
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO131" t="inlineStr">
+      <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP131" t="inlineStr">
+      <c r="AP133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR131" t="inlineStr">
+      <c r="AR133" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS131" t="inlineStr"/>
-      <c r="AT131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
+      <c r="AS133" t="inlineStr"/>
+      <c r="AT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV131" t="inlineStr">
+      <c r="AV133" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW131" t="inlineStr">
+      <c r="AW133" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
+      <c r="AX133" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY131" t="inlineStr">
+      <c r="AY133" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
+      <c r="AZ133" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA131" t="inlineStr">
+      <c r="BA133" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB131" t="inlineStr">
+      <c r="BB133" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC131" t="inlineStr">
+      <c r="BC133" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -25835,7 +26234,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -25845,7 +26244,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -25865,7 +26264,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1321,6 +1326,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3465,6 +3475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4412,6 +4427,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6157,6 +6177,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7104,6 +7129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9248,6 +9278,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9796,6 +9831,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11940,6 +11980,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12488,6 +12533,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15031,6 +15081,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15579,6 +15634,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17723,6 +17783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18271,6 +18336,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20415,6 +20485,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20963,6 +21038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23493,13 +23573,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O120" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R120" t="n">
-        <v>1.351894969856744</v>
+        <v>1.387471153274027</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23657,10 +23737,10 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O121" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -23909,6 +23989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24002,12 +24087,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -24032,7 +24117,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -24041,16 +24126,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>1.055971488396018</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -24059,12 +24141,12 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -24074,7 +24156,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
@@ -24082,57 +24164,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24164,12 +24251,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -24194,7 +24281,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -24203,32 +24290,29 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>TBE</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -24238,12 +24322,12 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
@@ -24253,7 +24337,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -24268,7 +24352,7 @@
       </c>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG124" t="inlineStr">
@@ -24288,17 +24372,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Japan NIID tick-borne encephalitis notifications.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM TBE disease category.</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -24311,7 +24395,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
@@ -24319,57 +24403,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_TBE</t>
         </is>
       </c>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24520,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -24593,7 +24682,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -24830,7 +24919,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -24992,7 +25081,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -25229,7 +25318,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -25391,7 +25480,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -25598,12 +25687,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -25628,22 +25717,25 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0.07115236683456549</v>
+        <v>0</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -25652,12 +25744,12 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -25667,70 +25759,65 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25762,12 +25849,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -25792,38 +25879,41 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>TBE (tick borne encephalitis)</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -25833,12 +25923,12 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
@@ -25848,7 +25938,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -25863,7 +25953,7 @@
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
@@ -25883,12 +25973,12 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
@@ -25906,70 +25996,65 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_708</t>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26001,118 +26086,526 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>11</v>
+      </c>
+      <c r="O133" t="n">
+        <v>11</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.1956690087950551</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>11</v>
+      </c>
+      <c r="O134" t="n">
+        <v>11</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>TBE (tick borne encephalitis)</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 708.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_708</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>D205</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Tick-borne encephalitis</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
         <is>
           <t>蜱传脑炎</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="K135" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="inlineStr">
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO133" t="inlineStr">
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP133" t="inlineStr">
+      <c r="AP135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR133" t="inlineStr">
+      <c r="AR135" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS133" t="inlineStr"/>
-      <c r="AT133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV133" t="inlineStr">
+      <c r="AV135" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW133" t="inlineStr">
+      <c r="AW135" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
+      <c r="AX135" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY133" t="inlineStr">
+      <c r="AY135" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
+      <c r="AZ135" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA133" t="inlineStr">
+      <c r="BA135" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB133" t="inlineStr">
+      <c r="BB135" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC133" t="inlineStr">
+      <c r="BC135" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -26234,7 +26727,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -26244,7 +26737,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -26264,7 +26757,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -26296,7 +26789,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1178</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O133" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R133" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -26289,10 +26289,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O134" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1300</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d205/2026-2029.xlsx
+++ b/diseases/d205/2026-2029.xlsx
@@ -24126,13 +24126,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O123" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R123" t="n">
-        <v>1.055971488396018</v>
+        <v>1.046626607967735</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -24290,10 +24290,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O124" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O133" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R133" t="n">
-        <v>0.284609467338262</v>
+        <v>0.3379737424641861</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -26289,10 +26289,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O134" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -26608,6 +26608,405 @@
       <c r="BC135" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>tick-borne-encephalitis</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Japan NIID tick-borne encephalitis notifications.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_JP_TICK_BORNE_ENCEPHALITIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26644,7 +27043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -26727,7 +27126,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -26737,7 +27136,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -26757,7 +27156,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -26789,7 +27188,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1305</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="16">
